--- a/data/file_generation/input/data_82/七年级标准.xlsx
+++ b/data/file_generation/input/data_82/七年级标准.xlsx
@@ -1557,26 +1557,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B181608A-F1B2-43D7-8179-030C693CF42D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7484836A-D248-4F17-9B95-4500DA47A4DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177D8A09-ADB3-4418-B8FF-4C61E82F821A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9D97AB-B0A4-4321-8C82-8C57A308FAA3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D9A2C43-261F-4092-B9D6-A313990B6987}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CB889D-279E-4F97-9F59-1705A69B0D12}"/>
 </file>